--- a/paper reading/papers.xlsx
+++ b/paper reading/papers.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31240" windowHeight="14800"/>
+    <workbookView windowHeight="17020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33">
   <si>
     <t>title</t>
   </si>
@@ -94,10 +94,25 @@
     <t>edge wise, node wise,</t>
   </si>
   <si>
-    <t>有证明</t>
+    <t>prove it</t>
   </si>
   <si>
     <t xml:space="preserve">两种稀疏矩阵乘法, </t>
+  </si>
+  <si>
+    <t>Design Space for Graph Neural Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. now specific model, we study different layer or agg function. 2.  single task now,  we quick find deisgn for new task or dataset.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">issue: 1 太specific 2 task 评估的太少3 对于node,edge 和graph没有统一范式. 提出了task space, evaluation 方法 </t>
+  </si>
+  <si>
+    <t>之前有了一些specific的研究, 一些evaluation的方法</t>
+  </si>
+  <si>
+    <t>graphGym可以用来复现和评估.</t>
   </si>
 </sst>
 </file>
@@ -105,10 +120,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -120,14 +135,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -141,23 +164,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -179,8 +187,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -189,6 +198,58 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -202,9 +263,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -212,54 +272,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -278,43 +293,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,7 +407,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -344,115 +461,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -466,11 +481,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -480,21 +501,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -510,36 +516,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -563,153 +539,192 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1036,8 +1051,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A5:P7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="17.6" outlineLevelRow="6"/>
+  <dimension ref="A5:P9"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="17.6"/>
   <sheetData>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
@@ -1130,6 +1145,26 @@
       </c>
       <c r="O7" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:15">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/paper reading/papers.xlsx
+++ b/paper reading/papers.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17020"/>
+    <workbookView windowWidth="30240" windowHeight="14800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68">
   <si>
     <t>title</t>
   </si>
@@ -49,6 +49,12 @@
     <t>Clarity: Is the paper well written?</t>
   </si>
   <si>
+    <t>关键词</t>
+  </si>
+  <si>
+    <t>我能学到什么</t>
+  </si>
+  <si>
     <t>pyg</t>
   </si>
   <si>
@@ -113,6 +119,135 @@
   </si>
   <si>
     <t>graphGym可以用来复现和评估.</t>
+  </si>
+  <si>
+    <t>DistDGL</t>
+  </si>
+  <si>
+    <t>it is DGL distributed module. use min-cut graph partitioning algorithm with multiple balancing constraints.replicating halo nodes &amp; using sparse embedding updates - 》 reduce communication</t>
+  </si>
+  <si>
+    <t>problem
+1.  depending sample.  needs sampling algorithm
+2.  major traffic  .  traditional :  gradient exchange vs  GNN:   neighbor vertex    . Difficult: generate same # node, edge.    imbalance!
+strategy
+1. synchronous approach.
+2.   network communication⬇️  =》METIS  topartition graph  (Ref:  A fast and high quality multilevel scheme for partitioning irregular graph)
+3. load balancing optimizations
+4. network communication⬇️  in sampling =》 replicate halo node √ data in halo node X</t>
+  </si>
+  <si>
+    <t>背景,  系统设计(图分的方法,  KV存储,分布式采样, trainer) 评估</t>
+  </si>
+  <si>
+    <t>多机</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ali Euler,METIS 分割图 </t>
+  </si>
+  <si>
+    <t>拓展性, 线性加速</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是一个范式. 不是服务器的优化. </t>
+  </si>
+  <si>
+    <t>OSDI2021</t>
+  </si>
+  <si>
+    <t>Dorylus</t>
+  </si>
+  <si>
+    <t>Computation separation makes it possible to construct a deep, bounded-asynchronous pipeline where graph and tensor parallel tasks can fully overlap.</t>
+  </si>
+  <si>
+    <t>Problem:
+1. CPUs memory enough, but   no parallelism
+2. sampling must be done repeatedly per epoch, time overhead ⬆️  and accuracy ⬇️, no convergene guarantee. 
+3. Lambda has network latency : 
+Assumption:
+1. *not all operations in GNN training need Lambda’s parallelism*
+2. Lambdas are a perfect fit to GNNs’ tensor computations (他说因为CPU贵, )
+Method
+1. graph-parallel (CPU instance) neighbor propagations (*e.g.*, Gather and Scatter) over the input graph.  d*ata gathering from neighbor vertices*
+2. tensor-parallel ( Lambdas) per-vertex/edge NN operations (such as Apply)  *parameter updates*
+3. network latency = 》   BPAC model, *bounded pipeline asynchronous computation,  fine grained task* 
+4. asynchrony slow down the convergence?  *bounds the degree of asynchrony*</t>
+  </si>
+  <si>
+    <t>introduction, background, 系统overview, 具体讲细节, 6讲了lambda的优化, 7讲了实验 8 相关工作</t>
+  </si>
+  <si>
+    <t>多机 An analysis of an existing system</t>
+  </si>
+  <si>
+    <t>1. use Lambdas , cheap 
+2. scalable solution on very large graph</t>
+  </si>
+  <si>
+    <t>serverless 针对GNN优化,</t>
+  </si>
+  <si>
+    <t>GNNadvisor</t>
+  </si>
+  <si>
+    <t>1. performance-relevant features from both the GNN model and the input graph(需要具体去看)
+2.  novel 2D work- load management 
+3. capitalizes on the GPU memory hierarchy</t>
+  </si>
+  <si>
+    <t>Problem⇒ method:
+1. one-size-fits-all,  no  optimize diverse GNN
+2.  not address the difference between GNN and graph processing =》 invoke more aggressive parallelism and more efficient memory optimization.  (why? )
+3. only static optimizations through a compiler or manually-optimized libraries    ⇒  runtime , node degree and embedding size 
+Design:
+torch as  front end 
+**Loader&amp;Extractor  find the input information,then optimize** 
+**Decider**     `Set runtime parameters automatically`
+**Kernel&amp;Runtime CrafterOnly 1 GPU**</t>
+  </si>
+  <si>
+    <t>3input分析, 4 workload管理 5 专用内存管理, 6 设计优化 7 实验</t>
+  </si>
+  <si>
+    <t xml:space="preserve">输入信息可以guide 优化方法, 比如内存管理和workload , 还有自动参数选择AutoML?   </t>
+  </si>
+  <si>
+    <t>单卡 An analysis of an existing system</t>
+  </si>
+  <si>
+    <t>探索了输入的特性 研究了workload 内存管理 1. explore GNN input properties
+2. a novel 2D workload management (§4) and specialized memory customization (§5) on GPUs.analytical model- ing and parameter auto-selection (§6)</t>
+  </si>
+  <si>
+    <t>Marius 马吕斯</t>
+  </si>
+  <si>
+    <t>减少数据移动的开销, 利用流水线 和caching.还有buffer aware data ordering</t>
+  </si>
+  <si>
+    <t>edge更新存放在GPU, 同步, node 更新存放在CPU,异步. 利用 caching, 来加快数据迁移</t>
+  </si>
+  <si>
+    <t>单机 存储系统的优化</t>
+  </si>
+  <si>
+    <t>提出减少IO的算法, 利用流水线和buffer.</t>
+  </si>
+  <si>
+    <t>introduction 可以列个表, asynchronous training</t>
+  </si>
+  <si>
+    <t>单机大图</t>
+  </si>
+  <si>
+    <t>学到 GNN的特性是怎么和存储系统影响的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3 </t>
+  </si>
+  <si>
+    <t>abstract 和introduction太冗长, 入门介绍部分太多,讲了两页没看出来到底干了啥.</t>
   </si>
 </sst>
 </file>
@@ -121,11 +256,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -134,9 +269,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -150,7 +301,91 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -165,91 +400,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,15 +423,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,73 +438,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,103 +618,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -481,76 +632,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -572,6 +658,71 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -583,154 +734,169 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1051,120 +1217,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A5:P9"/>
+  <dimension ref="A3:R13"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="17.6"/>
+  <cols>
+    <col min="16" max="16" width="22.7678571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="5" spans="1:16">
+    <row r="3" ht="23.2" spans="1:18">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J5" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N5" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="O5" t="s">
-        <v>9</v>
-      </c>
-      <c r="P5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" t="s">
-        <v>17</v>
-      </c>
-      <c r="N6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P6" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="O7" t="s">
-        <v>27</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1" spans="1:17">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:15">
       <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" t="s">
-        <v>16</v>
-      </c>
-      <c r="M9" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" t="s">
-        <v>32</v>
+        <v>43</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" ht="67" customHeight="1" spans="1:17">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" t="s">
+        <v>48</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1" spans="1:15">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" t="s">
+        <v>56</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" ht="69" customHeight="1" spans="1:18">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="L12" t="s">
+        <v>61</v>
+      </c>
+      <c r="O12" t="s">
+        <v>62</v>
+      </c>
+      <c r="P12" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>64</v>
+      </c>
+      <c r="R12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" ht="84" customHeight="1" spans="1:16">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" t="s">
+        <v>39</v>
+      </c>
+      <c r="P13" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
